--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:20+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:47:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:47:47+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:20+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -508,7 +508,7 @@
     <t>The business identifier for this task.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">exists:system}
 </t>
   </si>
   <si>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>87</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -508,7 +508,7 @@
     <t>The business identifier for this task.</t>
   </si>
   <si>
-    <t xml:space="preserve">exists:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>87</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3819" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3819" uniqueCount="633">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,9 +513,6 @@
   </si>
   <si>
     <t>Slice based on the type of identifier.</t>
-  </si>
-  <si>
-    <t>openAtEnd</t>
   </si>
   <si>
     <t>Request.identifier, Event.identifier</t>
@@ -3688,7 +3685,7 @@
         <v>77</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>153</v>
@@ -3706,13 +3703,13 @@
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -3720,13 +3717,13 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>153</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
@@ -3820,13 +3817,13 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3834,10 +3831,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3863,10 +3860,10 @@
         <v>89</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3917,28 +3914,28 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AG14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI14" t="s" s="2">
+      <c r="AJ14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -3946,10 +3943,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3975,10 +3972,10 @@
         <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
         <v>150</v>
@@ -4022,7 +4019,7 @@
         <v>137</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
@@ -4031,7 +4028,7 @@
         <v>138</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4052,7 +4049,7 @@
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -4060,10 +4057,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4089,16 +4086,16 @@
         <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -4126,28 +4123,28 @@
         <v>111</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4168,7 +4165,7 @@
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>132</v>
@@ -4176,10 +4173,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4202,19 +4199,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -4239,31 +4236,31 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4284,18 +4281,18 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4321,10 +4318,10 @@
         <v>89</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4375,28 +4372,28 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI18" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI18" t="s" s="2">
+      <c r="AJ18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -4404,10 +4401,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4433,10 +4430,10 @@
         <v>134</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>150</v>
@@ -4480,7 +4477,7 @@
         <v>137</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
@@ -4489,7 +4486,7 @@
         <v>138</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4510,7 +4507,7 @@
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -4518,10 +4515,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4544,19 +4541,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -4605,7 +4602,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4626,18 +4623,18 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4663,10 +4660,10 @@
         <v>89</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4717,28 +4714,28 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI21" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI21" t="s" s="2">
+      <c r="AJ21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4746,10 +4743,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4775,10 +4772,10 @@
         <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>150</v>
@@ -4822,7 +4819,7 @@
         <v>137</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
@@ -4831,7 +4828,7 @@
         <v>138</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4852,7 +4849,7 @@
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4860,10 +4857,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4889,16 +4886,16 @@
         <v>101</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4908,46 +4905,46 @@
         <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4968,18 +4965,18 @@
         <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5002,16 +4999,16 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5061,7 +5058,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5082,18 +5079,18 @@
         <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>236</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5119,14 +5116,14 @@
         <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -5136,7 +5133,7 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>77</v>
@@ -5175,16 +5172,16 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI25" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>99</v>
@@ -5196,18 +5193,18 @@
         <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5230,17 +5227,17 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -5250,47 +5247,47 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="T26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
@@ -5298,7 +5295,7 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>99</v>
@@ -5310,18 +5307,18 @@
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5344,19 +5341,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5405,7 +5402,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5426,18 +5423,18 @@
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5460,19 +5457,19 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5482,46 +5479,46 @@
         <v>77</v>
       </c>
       <c r="S28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5542,18 +5539,18 @@
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5579,65 +5576,65 @@
         <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T29" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="S29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T29" t="s" s="2">
+      <c r="U29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5658,18 +5655,18 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5692,16 +5689,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5715,52 +5712,52 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="U30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI30" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -5772,18 +5769,18 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5806,13 +5803,13 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5863,7 +5860,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5884,18 +5881,18 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>303</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5918,16 +5915,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5977,7 +5974,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5998,18 +5995,18 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6032,17 +6029,17 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -6091,7 +6088,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6106,13 +6103,13 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -6120,10 +6117,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6149,14 +6146,14 @@
         <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6205,7 +6202,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6220,13 +6217,13 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -6234,10 +6231,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6260,16 +6257,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6319,7 +6316,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6334,13 +6331,13 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -6348,10 +6345,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6377,14 +6374,14 @@
         <v>154</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6433,7 +6430,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6448,13 +6445,13 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6462,10 +6459,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6488,19 +6485,19 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6549,7 +6546,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6564,13 +6561,13 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6578,10 +6575,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6607,14 +6604,14 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6642,10 +6639,10 @@
         <v>111</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6663,7 +6660,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>87</v>
@@ -6678,13 +6675,13 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6692,10 +6689,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6718,16 +6715,16 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6757,7 +6754,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6775,7 +6772,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6796,7 +6793,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6804,10 +6801,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6833,10 +6830,10 @@
         <v>89</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6887,28 +6884,28 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI40" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI40" t="s" s="2">
+      <c r="AJ40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6916,10 +6913,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6945,10 +6942,10 @@
         <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>150</v>
@@ -6992,7 +6989,7 @@
         <v>137</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>77</v>
@@ -7001,7 +6998,7 @@
         <v>138</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7022,7 +7019,7 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -7030,10 +7027,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7056,13 +7053,13 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7113,7 +7110,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7142,10 +7139,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7171,10 +7168,10 @@
         <v>89</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7225,28 +7222,28 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI43" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI43" t="s" s="2">
+      <c r="AJ43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -7254,10 +7251,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7283,10 +7280,10 @@
         <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>150</v>
@@ -7330,7 +7327,7 @@
         <v>137</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>77</v>
@@ -7339,7 +7336,7 @@
         <v>138</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7360,7 +7357,7 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -7368,10 +7365,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7394,19 +7391,19 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -7455,7 +7452,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7476,18 +7473,18 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7510,19 +7507,19 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7532,7 +7529,7 @@
         <v>77</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>77</v>
@@ -7571,7 +7568,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7592,18 +7589,18 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7626,13 +7623,13 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7683,7 +7680,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7712,10 +7709,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7738,17 +7735,17 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7773,11 +7770,11 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="Y48" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="Z48" t="s" s="2">
         <v>77</v>
       </c>
@@ -7797,7 +7794,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7818,7 +7815,7 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7826,10 +7823,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7855,13 +7852,13 @@
         <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7872,7 +7869,7 @@
         <v>77</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>77</v>
@@ -7890,11 +7887,11 @@
         <v>111</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7911,7 +7908,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>87</v>
@@ -7926,13 +7923,13 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7940,10 +7937,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7969,20 +7966,20 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q50" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q50" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="R50" t="s" s="2">
         <v>77</v>
@@ -8006,11 +8003,11 @@
         <v>111</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
       </c>
@@ -8027,7 +8024,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8042,13 +8039,13 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -8056,10 +8053,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8082,16 +8079,16 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8141,7 +8138,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8156,13 +8153,13 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -8170,10 +8167,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8196,16 +8193,16 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8231,52 +8228,52 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="Z52" t="s" s="2">
+      <c r="AA52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI52" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -8284,10 +8281,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8310,13 +8307,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8367,7 +8364,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8388,7 +8385,7 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -8396,10 +8393,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8422,19 +8419,19 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8483,7 +8480,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8492,7 +8489,7 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>99</v>
@@ -8501,10 +8498,10 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8512,14 +8509,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8538,17 +8535,17 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8597,7 +8594,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8612,13 +8609,13 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8626,10 +8623,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8652,17 +8649,17 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8711,7 +8708,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8726,13 +8723,13 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AM56" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8740,10 +8737,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8766,16 +8763,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8825,7 +8822,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8840,13 +8837,13 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8854,10 +8851,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8880,13 +8877,13 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8937,7 +8934,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8952,13 +8949,13 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="AM58" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8966,14 +8963,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8992,17 +8989,17 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9051,7 +9048,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9060,19 +9057,19 @@
         <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -9080,14 +9077,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9106,17 +9103,17 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9165,7 +9162,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9174,7 +9171,7 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>99</v>
@@ -9186,7 +9183,7 @@
         <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -9194,10 +9191,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9220,17 +9217,17 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9279,7 +9276,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9294,13 +9291,13 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -9308,10 +9305,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9334,17 +9331,17 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9369,14 +9366,14 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="Y62" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="Y62" t="s" s="2">
+      <c r="Z62" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>486</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
       </c>
@@ -9393,7 +9390,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9408,13 +9405,13 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -9422,14 +9419,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9448,19 +9445,19 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9509,7 +9506,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9524,13 +9521,13 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -9538,10 +9535,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9564,13 +9561,13 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9621,7 +9618,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9650,10 +9647,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9676,13 +9673,13 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9733,28 +9730,28 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI65" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI65" t="s" s="2">
+      <c r="AJ65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>77</v>
@@ -9762,10 +9759,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9791,10 +9788,10 @@
         <v>134</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>150</v>
@@ -9847,7 +9844,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9868,7 +9865,7 @@
         <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -9876,14 +9873,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9905,10 +9902,10 @@
         <v>134</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>150</v>
@@ -9963,7 +9960,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9992,10 +9989,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10018,13 +10015,13 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10051,10 +10048,10 @@
         <v>77</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>77</v>
@@ -10075,7 +10072,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10104,10 +10101,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10130,13 +10127,13 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10187,7 +10184,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>87</v>
@@ -10216,10 +10213,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10242,19 +10239,19 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -10303,7 +10300,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10321,10 +10318,10 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -10332,10 +10329,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10358,16 +10355,16 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10393,10 +10390,10 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>77</v>
@@ -10417,7 +10414,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10432,24 +10429,24 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AM71" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10472,13 +10469,13 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10529,7 +10526,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10544,24 +10541,24 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="AL72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>540</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10584,13 +10581,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10641,7 +10638,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10656,13 +10653,13 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -10670,14 +10667,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10696,16 +10693,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10755,7 +10752,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10770,13 +10767,13 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>77</v>
@@ -10784,10 +10781,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10810,19 +10807,19 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -10871,7 +10868,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10880,7 +10877,7 @@
         <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>99</v>
@@ -10892,7 +10889,7 @@
         <v>77</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>77</v>
@@ -10900,10 +10897,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10926,13 +10923,13 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10983,28 +10980,28 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI76" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AG76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI76" t="s" s="2">
+      <c r="AJ76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>77</v>
@@ -11012,10 +11009,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11041,10 +11038,10 @@
         <v>134</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>150</v>
@@ -11097,7 +11094,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11118,7 +11115,7 @@
         <v>77</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>77</v>
@@ -11126,14 +11123,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11155,10 +11152,10 @@
         <v>134</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>150</v>
@@ -11213,7 +11210,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11242,10 +11239,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11268,17 +11265,17 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11327,7 +11324,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11348,7 +11345,7 @@
         <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
@@ -11356,10 +11353,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11382,19 +11379,19 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -11443,7 +11440,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11464,7 +11461,7 @@
         <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>77</v>
@@ -11472,10 +11469,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11498,13 +11495,13 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11555,7 +11552,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11576,7 +11573,7 @@
         <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>77</v>
@@ -11584,14 +11581,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11610,17 +11607,17 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -11669,7 +11666,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11690,7 +11687,7 @@
         <v>77</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>77</v>
@@ -11698,10 +11695,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11724,13 +11721,13 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11781,28 +11778,28 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI83" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AG83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI83" t="s" s="2">
+      <c r="AJ83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>77</v>
@@ -11810,10 +11807,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11839,10 +11836,10 @@
         <v>134</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>150</v>
@@ -11895,7 +11892,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11916,7 +11913,7 @@
         <v>77</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>77</v>
@@ -11924,14 +11921,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -11953,10 +11950,10 @@
         <v>134</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>150</v>
@@ -12011,7 +12008,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12040,14 +12037,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12066,19 +12063,19 @@
         <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -12103,10 +12100,10 @@
         <v>77</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="Z86" t="s" s="2">
         <v>77</v>
@@ -12127,7 +12124,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>87</v>
@@ -12148,7 +12145,7 @@
         <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>77</v>
@@ -12156,10 +12153,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12182,13 +12179,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12239,7 +12236,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>87</v>
@@ -12260,7 +12257,7 @@
         <v>77</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>77</v>
@@ -12268,10 +12265,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12294,17 +12291,17 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -12353,7 +12350,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12374,7 +12371,7 @@
         <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>77</v>
@@ -12382,10 +12379,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12408,13 +12405,13 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12465,28 +12462,28 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI89" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AG89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI89" t="s" s="2">
+      <c r="AJ89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>77</v>
@@ -12494,10 +12491,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12523,10 +12520,10 @@
         <v>134</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>150</v>
@@ -12579,7 +12576,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12600,7 +12597,7 @@
         <v>77</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>77</v>
@@ -12608,14 +12605,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12637,10 +12634,10 @@
         <v>134</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>150</v>
@@ -12695,7 +12692,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12724,14 +12721,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12750,17 +12747,17 @@
         <v>77</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -12785,10 +12782,10 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Z92" t="s" s="2">
         <v>77</v>
@@ -12809,7 +12806,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>87</v>
@@ -12830,7 +12827,7 @@
         <v>77</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>77</v>
@@ -12838,10 +12835,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12867,10 +12864,10 @@
         <v>89</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12921,28 +12918,28 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI93" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AG93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI93" t="s" s="2">
+      <c r="AJ93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>77</v>
@@ -12950,10 +12947,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12979,10 +12976,10 @@
         <v>134</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>150</v>
@@ -13026,7 +13023,7 @@
         <v>137</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>77</v>
@@ -13035,7 +13032,7 @@
         <v>138</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13056,7 +13053,7 @@
         <v>77</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>77</v>
@@ -13064,10 +13061,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13090,19 +13087,19 @@
         <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -13151,7 +13148,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13172,18 +13169,18 @@
         <v>77</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13209,10 +13206,10 @@
         <v>89</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13263,28 +13260,28 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI96" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AG96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI96" t="s" s="2">
+      <c r="AJ96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>77</v>
@@ -13292,10 +13289,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13321,10 +13318,10 @@
         <v>134</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>150</v>
@@ -13368,7 +13365,7 @@
         <v>137</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>77</v>
@@ -13377,7 +13374,7 @@
         <v>138</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13398,7 +13395,7 @@
         <v>77</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>77</v>
@@ -13406,10 +13403,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13435,16 +13432,16 @@
         <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13493,7 +13490,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13514,18 +13511,18 @@
         <v>77</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>227</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13548,16 +13545,16 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13607,7 +13604,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13628,18 +13625,18 @@
         <v>77</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>236</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13665,14 +13662,14 @@
         <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -13701,7 +13698,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>77</v>
@@ -13719,16 +13716,16 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI100" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>99</v>
@@ -13740,18 +13737,18 @@
         <v>77</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13774,17 +13771,17 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -13833,7 +13830,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13842,7 +13839,7 @@
         <v>87</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>99</v>
@@ -13854,18 +13851,18 @@
         <v>77</v>
       </c>
       <c r="AM101" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13888,19 +13885,19 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -13949,7 +13946,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13970,18 +13967,18 @@
         <v>77</v>
       </c>
       <c r="AM102" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14004,19 +14001,19 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -14026,7 +14023,7 @@
         <v>77</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>77</v>
@@ -14065,7 +14062,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14086,18 +14083,18 @@
         <v>77</v>
       </c>
       <c r="AM103" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14120,17 +14117,17 @@
         <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -14167,17 +14164,17 @@
         <v>77</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AC104" s="2"/>
       <c r="AD104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>87</v>
@@ -14198,7 +14195,7 @@
         <v>77</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>77</v>
@@ -14206,13 +14203,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="C105" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>77</v>
@@ -14234,17 +14231,17 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -14293,7 +14290,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>87</v>
@@ -14314,7 +14311,7 @@
         <v>77</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>77</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-lab-task</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/hiv-lab-task</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
     <t>ResultStatusIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/result-status-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/result-status-index}
 </t>
   </si>
   <si>
@@ -1122,7 +1122,7 @@
     <t>This applies to the current status.  Look at the history of the task to see reasons for past statuses.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-sample-cancelled-or-rejected</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-reason-sample-cancelled-or-rejected</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
@@ -1941,7 +1941,7 @@
     <t>Task.output.type.coding.code</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-vl-result-code</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-vl-result-code</t>
   </si>
   <si>
     <t>Task.output.type.coding.display</t>
@@ -2331,7 +2331,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.0390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="125.3203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/hiv-lab-task</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-lab-task</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
     <t>ResultStatusIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/result-status-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/result-status-index}
 </t>
   </si>
   <si>
@@ -1122,7 +1122,7 @@
     <t>This applies to the current status.  Look at the history of the task to see reasons for past statuses.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-reason-sample-cancelled-or-rejected</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-sample-cancelled-or-rejected</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
@@ -1941,7 +1941,7 @@
     <t>Task.output.type.coding.code</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-vl-result-code</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-vl-result-code</t>
   </si>
   <si>
     <t>Task.output.type.coding.display</t>
@@ -2331,7 +2331,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="125.3203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.0390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:25:42+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-lab-task</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/hiv-lab-task</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
     <t>ResultStatusIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/result-status-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/result-status-index}
 </t>
   </si>
   <si>
@@ -1122,7 +1122,7 @@
     <t>This applies to the current status.  Look at the history of the task to see reasons for past statuses.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-sample-cancelled-or-rejected</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-reason-sample-cancelled-or-rejected</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
@@ -1941,7 +1941,7 @@
     <t>Task.output.type.coding.code</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-vl-result-code</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-vl-result-code</t>
   </si>
   <si>
     <t>Task.output.type.coding.display</t>
@@ -2331,7 +2331,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.0390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="120.9921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/hiv-lab-task</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-lab-task</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
     <t>ResultStatusIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/result-status-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/result-status-index}
 </t>
   </si>
   <si>
@@ -1122,7 +1122,7 @@
     <t>This applies to the current status.  Look at the history of the task to see reasons for past statuses.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-reason-sample-cancelled-or-rejected</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-sample-cancelled-or-rejected</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
@@ -1941,7 +1941,7 @@
     <t>Task.output.type.coding.code</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-vl-result-code</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-vl-result-code</t>
   </si>
   <si>
     <t>Task.output.type.coding.display</t>
@@ -2331,7 +2331,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="120.9921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.0390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:14+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-hiv-lab-task.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
